--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Nombre</t>
   </si>
@@ -63,21 +63,12 @@
 Una vez Vida se haya recuperado esperamos encontrar una familia que pueda ofrecerle todo el cariño que se merece. Por el momento puedes apadrinarla o participar en nuestra rifa solidaria para financiar su tratamiento médico</t>
   </si>
   <si>
-    <t>7 años</t>
-  </si>
-  <si>
-    <t>Mix yorki</t>
-  </si>
-  <si>
     <t>hembra mix yorki</t>
   </si>
   <si>
     <t>Sira</t>
   </si>
   <si>
-    <t>Está esterelizada y en Cádiz pero podemos transportarla a toda España</t>
-  </si>
-  <si>
     <t>Zule</t>
   </si>
   <si>
@@ -90,18 +81,7 @@
     <t>Hera</t>
   </si>
   <si>
-    <t>3 años y 9 meses</t>
-  </si>
-  <si>
-    <t>Podenco maneto de pata corta</t>
-  </si>
-  <si>
     <t>hera</t>
-  </si>
-  <si>
-    <t>13kg, ya no crece más._x000D_
-Esterelizada_x000D_
-Muy tranquila y acogedora. Convive muy bien con otros perros y personas</t>
   </si>
   <si>
     <t>Negra</t>
@@ -625,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
@@ -661,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -673,125 +653,79 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -801,7 +735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -816,102 +750,118 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>18</v>
       </c>
     </row>
@@ -930,7 +880,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B1">
         <v>649776448</v>
@@ -938,7 +888,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>692160589</v>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t>Nombre</t>
   </si>
@@ -209,6 +209,22 @@
   </si>
   <si>
     <t>2 años</t>
+  </si>
+  <si>
+    <t>Merlo</t>
+  </si>
+  <si>
+    <t>merlo</t>
+  </si>
+  <si>
+    <t>mix Podenco</t>
+  </si>
+  <si>
+    <t>2 semanas</t>
+  </si>
+  <si>
+    <t>La madre es un podenco maneto y se desconoce al padre.
+Se entrega con protocolo veterinario completo y puede viajar a casi toda España</t>
   </si>
 </sst>
 </file>
@@ -605,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
@@ -726,6 +742,29 @@
       </c>
       <c r="G5" s="2" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -223,7 +223,8 @@
     <t>2 semanas</t>
   </si>
   <si>
-    <t>La madre es un podenco maneto y se desconoce al padre.
+    <t>Merlo es el cachorro del medio.
+La madre es un podenco maneto y se desconoce al padre.
 Se entrega con protocolo veterinario completo y puede viajar a casi toda España</t>
   </si>
 </sst>
@@ -744,7 +745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>

--- a/assets/database/Animales.xlsx
+++ b/assets/database/Animales.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
   <si>
     <t>Nombre</t>
   </si>
@@ -123,22 +123,9 @@
     <t>Camada</t>
   </si>
   <si>
-    <t>3 semanas</t>
-  </si>
-  <si>
-    <t>variado</t>
-  </si>
-  <si>
-    <t>mix American Standfor y Pitbull</t>
-  </si>
-  <si>
     <t>camada amerian standfor pitbull</t>
   </si>
   <si>
-    <t>Podrán viajar y entregarse a mediados de octubre_x000D_
-La hembra gris ya esta adoptada</t>
-  </si>
-  <si>
     <t>Carpeta</t>
   </si>
   <si>
@@ -223,9 +210,11 @@
     <t>2 semanas</t>
   </si>
   <si>
-    <t>Merlo es el cachorro del medio.
-La madre es un podenco maneto y se desconoce al padre.
+    <t>La madre es un podenco maneto y se desconoce al padre.
 Se entrega con protocolo veterinario completo y puede viajar a casi toda España</t>
+  </si>
+  <si>
+    <t>Camada amerian standfor y pitbull</t>
   </si>
 </sst>
 </file>
@@ -622,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.85546875" style="3" customWidth="1"/>
@@ -658,7 +647,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -722,50 +711,27 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="G5" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -775,7 +741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" customWidth="1"/>
@@ -785,103 +751,103 @@
     <col min="5" max="5" width="66" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>48</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>52</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -889,20 +855,28 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
